--- a/sheets/민요/검수/이별가.xlsx
+++ b/sheets/민요/검수/이별가.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,42 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3232,8 +3348,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:K18"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -3246,776 +3366,713 @@
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이별가 — 민요채보-1/이별가.jpg</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">이별가</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">님</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" s="16"/>
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E4" s="16"/>
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G4" s="16"/>
+      <c r="H4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="I4" s="16"/>
+      <c r="J4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K4" s="2"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="K4" s="16"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">과</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K5" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">별</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="17"/>
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E6" s="17"/>
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G6" s="17"/>
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="I6" s="17"/>
+      <c r="J6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K6" s="2"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="K6" s="17"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="C8" s="16"/>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E8" s="16"/>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G8" s="16"/>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I8" s="16"/>
+      <c r="J8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K8" s="2"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="K8" s="16"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" s="17"/>
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G10" s="17"/>
+      <c r="H10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="I10" s="17"/>
+      <c r="J10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="K10" s="17"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">날</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="13"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="E12" s="16"/>
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G12" s="16"/>
+      <c r="H12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="I12" s="16"/>
+      <c r="J12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K12" s="2"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="K12" s="16"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">과</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">湳</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" s="17"/>
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="E14" s="17"/>
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G14" s="17"/>
+      <c r="H14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="I14" s="17"/>
+      <c r="J14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K14" s="17"/>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="B15" s="13"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">별</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2" t="inlineStr">
+    <row r="16" ht="56" customHeight="1">
+      <c r="B16" s="13"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="E16" s="16"/>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G16" s="16"/>
+      <c r="H16" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="I16" s="16"/>
+      <c r="J16" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K16" s="2"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="1">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K16" s="16"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="13"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K17" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="1">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="5" t="inlineStr">
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="13"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">古</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">별</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G18" s="17"/>
+      <c r="H18" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="I18" s="17"/>
+      <c r="J18" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K18" s="2"/>
+      <c r="K18" s="17"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:K2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="77"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/이별가.xlsx
+++ b/sheets/민요/검수/이별가.xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -553,12 +553,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|汰</t>
+          <t xml:space="preserve">–|汰</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -679,12 +679,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I5" s="2"/>
@@ -714,12 +714,12 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|汰</t>
+          <t xml:space="preserve">–|汰</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -867,12 +867,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南林</t>
+          <t xml:space="preserve">–南林</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南林</t>
+          <t xml:space="preserve">–南林</t>
         </is>
       </c>
       <c r="I25" s="2"/>
@@ -1504,13 +1504,13 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―</t>
+          <t xml:space="preserve">–|–</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="I26" s="3"/>
@@ -1700,12 +1700,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I31" s="2"/>
@@ -1774,12 +1774,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I33" s="2"/>
@@ -1852,12 +1852,12 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I35" s="2"/>
@@ -1887,12 +1887,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -2052,7 +2052,7 @@
       <c r="A4" s="0"/>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C4" s="9"/>
@@ -2114,7 +2114,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C6" s="10"/>
@@ -2126,7 +2126,7 @@
       <c r="E6" s="13"/>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G6" s="10"/>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="F7" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -2186,7 +2186,7 @@
       <c r="A9" s="0"/>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C9" s="9"/>
@@ -2232,7 +2232,7 @@
       <c r="A11" s="0"/>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -2271,7 +2271,7 @@
       <c r="C12" s="9"/>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―南林</t>
+          <t xml:space="preserve">–南林</t>
         </is>
       </c>
       <c r="E12" s="9"/>
@@ -2293,8 +2293,8 @@
       <c r="C13" s="9"/>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="E13" s="12"/>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="F15" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">

--- a/sheets/민요/검수/이별가.xlsx
+++ b/sheets/민요/검수/이별가.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2003,46 +2044,46 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">이별가</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林姑</t>
         </is>
       </c>
-      <c r="C3" s="11" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이이</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="D3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -2050,28 +2091,28 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="C4" s="25"/>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林姑</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -2079,32 +2120,32 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南林</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">淋潢</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">이야</t>
         </is>
@@ -2112,54 +2153,54 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚</t>
         </is>
       </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G6" s="10"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G6" s="27"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아아</t>
         </is>
       </c>
-      <c r="F7" s="18" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -2167,95 +2208,95 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="B8" s="23"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢南潢</t>
         </is>
       </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="E8" s="26"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢淋</t>
         </is>
       </c>
-      <c r="G8" s="12"/>
+      <c r="G8" s="26"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="C9" s="25"/>
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢太</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">날</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G9" s="9"/>
+      <c r="G9" s="25"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="B10" s="23"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">과</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚</t>
         </is>
       </c>
-      <c r="G10" s="10"/>
+      <c r="G10" s="27"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아아</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아아</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -2263,25 +2304,25 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="25"/>
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–南林</t>
         </is>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="E12" s="25"/>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋汰
 㳞</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="G12" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아아아</t>
         </is>
@@ -2289,21 +2330,21 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="B13" s="23"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –</t>
         </is>
       </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="26"/>
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">淋潢</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">이별이</t>
         </is>
@@ -2311,53 +2352,53 @@
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="B14" s="23"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G14" s="13"/>
+      <c r="G14" s="28"/>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太潢姑</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이별이</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南姑</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">이별이</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">이이야</t>
         </is>
@@ -2365,20 +2406,20 @@
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="B16" s="23"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚</t>
         </is>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="E16" s="25"/>
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="G16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -2386,21 +2427,21 @@
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="9"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="25"/>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="10"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/이별가.xlsx
+++ b/sheets/민요/검수/이별가.xlsx
@@ -2031,18 +2031,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
       <c r="F2" s="20"/>
       <c r="G2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="G6" s="27"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="23"/>
       <c r="C8" s="25"/>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="G8" s="26"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="G9" s="25"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="23"/>
       <c r="C10" s="27"/>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="G10" s="27"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="23"/>
       <c r="C13" s="25"/>
@@ -2350,7 +2350,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23"/>
       <c r="C14" s="27"/>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="G14" s="28"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="55.19" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="55.19" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="23"/>
       <c r="C16" s="25"/>
@@ -2425,7 +2425,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="55.19" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="23"/>
       <c r="C17" s="25"/>
@@ -2434,7 +2434,7 @@
       <c r="F17" s="23"/>
       <c r="G17" s="25"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="55.19" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="23"/>
       <c r="C18" s="27"/>

--- a/sheets/민요/검수/이별가.xlsx
+++ b/sheets/민요/검수/이별가.xlsx
@@ -873,12 +873,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I9" s="2"/>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I19" s="3"/>
@@ -1663,12 +1663,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I29" s="2"/>
@@ -2161,7 +2161,7 @@
       <c r="C6" s="27"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E6" s="28"/>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="F10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G10" s="27"/>
@@ -2410,7 +2410,7 @@
       <c r="C16" s="25"/>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">⁚</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E16" s="25"/>

--- a/sheets/민요/검수/이별가.xlsx
+++ b/sheets/민요/검수/이별가.xlsx
@@ -2064,7 +2064,8 @@
       </c>
       <c r="C3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">이이</t>
+          <t xml:space="preserve">이
+이</t>
         </is>
       </c>
       <c r="D3" s="23" t="inlineStr">
@@ -2147,7 +2148,8 @@
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">이야</t>
+          <t xml:space="preserve">이
+야</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2193,8 @@
       </c>
       <c r="E7" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">아아</t>
+          <t xml:space="preserve">아
+아</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -2278,7 +2281,8 @@
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">아아</t>
+          <t xml:space="preserve">아
+아</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -2288,7 +2292,8 @@
       </c>
       <c r="E11" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">아아</t>
+          <t xml:space="preserve">아
+아</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
@@ -2324,7 +2329,9 @@
       </c>
       <c r="G12" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">아아아</t>
+          <t xml:space="preserve">아
+아
+아</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2353,9 @@
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">이별이</t>
+          <t xml:space="preserve">이
+별
+이</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2389,9 @@
       </c>
       <c r="C15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">이별이</t>
+          <t xml:space="preserve">이
+별
+이</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -2390,7 +2401,9 @@
       </c>
       <c r="E15" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">이별이</t>
+          <t xml:space="preserve">이
+별
+이</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
@@ -2400,7 +2413,9 @@
       </c>
       <c r="G15" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">이이야</t>
+          <t xml:space="preserve">이
+이
+야</t>
         </is>
       </c>
     </row>

--- a/sheets/민요/검수/이별가.xlsx
+++ b/sheets/민요/검수/이별가.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -234,6 +239,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2062,7 +2085,7 @@
           <t xml:space="preserve">南林姑</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 이</t>
@@ -2073,7 +2096,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E3" s="24" t="inlineStr">
+      <c r="E3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -2084,7 +2107,7 @@
 汰</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -2097,13 +2120,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C4" s="25"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南林姑</t>
         </is>
       </c>
-      <c r="E4" s="26" t="inlineStr">
+      <c r="E4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -2113,7 +2136,7 @@
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="G4" s="26" t="inlineStr">
+      <c r="G4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -2126,7 +2149,7 @@
           <t xml:space="preserve">南林</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -2136,7 +2159,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -2146,7 +2169,7 @@
           <t xml:space="preserve">淋潢</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 야</t>
@@ -2160,19 +2183,19 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C6" s="27"/>
+      <c r="C6" s="33"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="E6" s="28"/>
+      <c r="E6" s="34"/>
       <c r="F6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G6" s="27"/>
+      <c r="G6" s="33"/>
     </row>
     <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
@@ -2181,7 +2204,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -2191,7 +2214,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E7" s="24" t="inlineStr">
+      <c r="E7" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 아</t>
@@ -2203,7 +2226,7 @@
 汰</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -2212,19 +2235,19 @@
     <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="23"/>
-      <c r="C8" s="25"/>
+      <c r="C8" s="31"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢南潢</t>
         </is>
       </c>
-      <c r="E8" s="26"/>
+      <c r="E8" s="32"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢淋</t>
         </is>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="32"/>
     </row>
     <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
@@ -2233,13 +2256,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C9" s="25"/>
+      <c r="C9" s="31"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰潢太</t>
         </is>
       </c>
-      <c r="E9" s="26" t="inlineStr">
+      <c r="E9" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">날</t>
         </is>
@@ -2249,18 +2272,18 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G9" s="25"/>
+      <c r="G9" s="31"/>
     </row>
     <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="23"/>
-      <c r="C10" s="27"/>
+      <c r="C10" s="33"/>
       <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E10" s="27" t="inlineStr">
+      <c r="E10" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">과</t>
         </is>
@@ -2270,7 +2293,7 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G10" s="27"/>
+      <c r="G10" s="33"/>
     </row>
     <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
@@ -2279,7 +2302,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 아</t>
@@ -2290,7 +2313,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E11" s="24" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 아</t>
@@ -2301,7 +2324,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G11" s="24" t="inlineStr">
+      <c r="G11" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -2314,20 +2337,20 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C12" s="25"/>
+      <c r="C12" s="31"/>
       <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–南林</t>
         </is>
       </c>
-      <c r="E12" s="25"/>
+      <c r="E12" s="31"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋汰
 㳞</t>
         </is>
       </c>
-      <c r="G12" s="26" t="inlineStr">
+      <c r="G12" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 아
@@ -2338,20 +2361,20 @@
     <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="23"/>
-      <c r="C13" s="25"/>
+      <c r="C13" s="31"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –</t>
         </is>
       </c>
-      <c r="E13" s="26"/>
+      <c r="E13" s="32"/>
       <c r="F13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">淋潢</t>
         </is>
       </c>
-      <c r="G13" s="25" t="inlineStr">
+      <c r="G13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 별
@@ -2362,13 +2385,13 @@
     <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23"/>
-      <c r="C14" s="27"/>
+      <c r="C14" s="33"/>
       <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E14" s="27" t="inlineStr">
+      <c r="E14" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -2378,7 +2401,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="G14" s="28"/>
+      <c r="G14" s="34"/>
     </row>
     <row r="15" ht="55.19" customHeight="1">
       <c r="A15" s="0"/>
@@ -2387,7 +2410,7 @@
           <t xml:space="preserve">太潢姑</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 별
@@ -2399,7 +2422,7 @@
           <t xml:space="preserve">南姑</t>
         </is>
       </c>
-      <c r="E15" s="24" t="inlineStr">
+      <c r="E15" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 별
@@ -2411,7 +2434,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G15" s="24" t="inlineStr">
+      <c r="G15" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 이
@@ -2422,19 +2445,19 @@
     <row r="16" ht="55.19" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="23"/>
-      <c r="C16" s="25"/>
+      <c r="C16" s="31"/>
       <c r="D16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="E16" s="25"/>
+      <c r="E16" s="31"/>
       <c r="F16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="G16" s="25" t="inlineStr">
+      <c r="G16" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -2443,20 +2466,20 @@
     <row r="17" ht="55.19" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="23"/>
-      <c r="C17" s="25"/>
+      <c r="C17" s="31"/>
       <c r="D17" s="23"/>
-      <c r="E17" s="25"/>
+      <c r="E17" s="31"/>
       <c r="F17" s="23"/>
-      <c r="G17" s="25"/>
+      <c r="G17" s="31"/>
     </row>
     <row r="18" ht="55.19" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="23"/>
-      <c r="C18" s="27"/>
+      <c r="C18" s="33"/>
       <c r="D18" s="23"/>
-      <c r="E18" s="27"/>
+      <c r="E18" s="33"/>
       <c r="F18" s="23"/>
-      <c r="G18" s="27"/>
+      <c r="G18" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/이별가.xlsx
+++ b/sheets/민요/검수/이별가.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -217,46 +212,28 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -329,7 +306,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/4 / 16정간</t>
+          <t xml:space="preserve">4/4 / 8정간</t>
         </is>
       </c>
     </row>
@@ -353,7 +330,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
     </row>
@@ -365,7 +342,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
     </row>
@@ -389,7 +366,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">중</t>
+          <t xml:space="preserve">상</t>
         </is>
       </c>
     </row>
@@ -399,11 +376,7 @@
           <t xml:space="preserve">확인 필요</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비고 41%</t>
-        </is>
-      </c>
+      <c r="B12" s="4"/>
     </row>
     <row r="13">
       <c r="A13" s="0"/>
@@ -429,7 +402,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">인쇄 양식, 위에 줄 번호(오른쪽 1), 왼쪽에 정간 번호 1~16, 번호 2개(1·2,3·4…)가 한 칸→위 절반=홀수, 아래 절반=짝수. 굵은 선 4칸마다 → 4/4·16. 오른쪽 여백에 제목 "이별가", 아래 "느릿 굿거리", "노래따라" 표기. 가장 오른쪽 인쇄 열(번호 1)은 비어 있어 내용 있는 첫 열을 줄1로 셈. 전곡에 걸쳐 율명 오른쪽에 s자·3자 꾸밈음과 물결선 } , 닫는 곡선 ) 모양의 요성 표시가 많은데 기호표에 없어 율명에서 빼고 비고로 남김(해당 칸 거의 전부라 일일이 적지 않고 여기 총괄 기록). 멜리스마 모음(아·이·야)이 가사로 붙음. 매우 빽빽해 겹친 율명 판독 불확실. AI 재판독 초안.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 16정간 인쇄 양식(196)이지만 번호 2개(1·2,3·4…)씩 큰 칸 8개로 쓰고 칸마다 율명 2~3개 → 큰 칸 1개 = 정간 1개, 4/4·8(는실 타령 양식). 맨 오른쪽 인쇄 열(1)은 비어 열2를 줄1로, 열2~5 = 줄1~4, 열6~8 빈 줄 제외. 오른쪽 여백에 "이별가", "느릿 굿거리", "노래따라". 율명 오른쪽 작은 3자·s자 꾸밈(汰·潢·南 등)과 칸 사이 세로 물결선·닫는 곡선 요성 표시는 기호표에 없어 생략, 꺾쇠 모양만 ^. 가사 칸의 늘임 ㅣ 는 생략. 멜리스마 모음(아·이)이 가사로 붙음.</t>
         </is>
       </c>
     </row>
@@ -615,27 +588,24 @@
       <c r="F2" s="2">
         <v>1</v>
       </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|汰</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-汰</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰 오른쪽 s자 꾸밈</t>
-        </is>
-      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">淋|㴌|–</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">淋
+㴌
+–</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이별</t>
+        </is>
+      </c>
+      <c r="J2" s="4"/>
       <c r="K2" s="2"/>
     </row>
     <row r="3">
@@ -659,26 +629,24 @@
       <c r="F3" s="2">
         <v>1</v>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢潢</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢潢</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢 두 개, 오른쪽 물결선 요성</t>
-        </is>
-      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|汰|潢㴌</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+汰
+潢㴌</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이이</t>
+        </is>
+      </c>
+      <c r="J3" s="4"/>
       <c r="K3" s="2"/>
     </row>
     <row r="4">
@@ -704,12 +672,14 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋潢</t>
+          <t xml:space="preserve">淋|㴌|–</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋潢</t>
+          <t xml:space="preserve">淋
+㴌
+–</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -743,15 +713,21 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–|汰|潢㴌</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I5" s="2"/>
+          <t xml:space="preserve">–
+汰
+潢㴌</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아아</t>
+        </is>
+      </c>
       <c r="J5" s="4"/>
       <c r="K5" s="2"/>
     </row>
@@ -776,27 +752,24 @@
       <c r="F6" s="2">
         <v>2</v>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|汰</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-汰</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰|–|–</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+–
+–</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰 s자 꾸밈</t>
-        </is>
-      </c>
+      <c r="J6" s="4"/>
       <c r="K6" s="2"/>
     </row>
     <row r="7">
@@ -822,18 +795,24 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢淋</t>
+          <t xml:space="preserve">–|㴌汰|㴌△</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢淋</t>
-        </is>
-      </c>
-      <c r="I7" s="3"/>
+          <t xml:space="preserve">–
+㴌汰
+㴌△</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아아아</t>
+        </is>
+      </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">닫는 곡선 ) 요성</t>
+          <t xml:space="preserve">아래 㴌 오른쪽 아래에 작은 △</t>
         </is>
       </c>
       <c r="K7" s="2"/>
@@ -861,15 +840,21 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">淋|㴌|汰</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I8" s="2"/>
+          <t xml:space="preserve">淋
+㴌
+汰</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이별이</t>
+        </is>
+      </c>
       <c r="J8" s="4"/>
       <c r="K8" s="2"/>
     </row>
@@ -894,18 +879,28 @@
       <c r="F9" s="2">
         <v>2</v>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="4"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|潢|㴌</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+潢
+㴌</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이이이</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">끝 가사 이/어?</t>
+        </is>
+      </c>
       <c r="K9" s="2"/>
     </row>
     <row r="10">
@@ -918,30 +913,32 @@
         </is>
       </c>
       <c r="C10" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">汰|–|潢</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">汰
+–
+潢</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">아</t>
+          <t xml:space="preserve">이이</t>
         </is>
       </c>
       <c r="J10" s="4"/>
@@ -957,38 +954,35 @@
         </is>
       </c>
       <c r="C11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F11" s="2">
-        <v>3</v>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋汰|㳞</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋汰
-㳞</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아아아</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">겹쳐 적혀 확실치 않음</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南林|姑|–△</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南林
+姑
+–△</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이야</t>
+        </is>
+      </c>
+      <c r="J11" s="4"/>
       <c r="K11" s="2"/>
     </row>
     <row r="12">
@@ -1001,30 +995,32 @@
         </is>
       </c>
       <c r="C12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="2">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F12" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋潢</t>
+          <t xml:space="preserve">南|–|·</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋潢</t>
+          <t xml:space="preserve">南
+–
+·</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이별이</t>
+          <t xml:space="preserve">아</t>
         </is>
       </c>
       <c r="J12" s="4"/>
@@ -1040,33 +1036,35 @@
         </is>
       </c>
       <c r="C13" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F13" s="2">
-        <v>3</v>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I13" s="3"/>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰 s자 꾸밈</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|–|潢</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+–
+潢</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="J13" s="4"/>
       <c r="K13" s="2"/>
     </row>
     <row r="14">
@@ -1079,30 +1077,32 @@
         </is>
       </c>
       <c r="C14" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F14" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">汰|–潢|南林</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">汰
+–潢
+南林</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이이야</t>
+          <t xml:space="preserve">아</t>
         </is>
       </c>
       <c r="J14" s="4"/>
@@ -1118,30 +1118,32 @@
         </is>
       </c>
       <c r="C15" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F15" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
+          <t xml:space="preserve">姑|–|南林</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
+          <t xml:space="preserve">姑
+–
+南林</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">아</t>
+          <t xml:space="preserve">아아</t>
         </is>
       </c>
       <c r="J15" s="4"/>
@@ -1163,26 +1165,24 @@
         <v>2</v>
       </c>
       <c r="E16" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F16" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">姑|–|△</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
+          <t xml:space="preserve">姑
+–
+△</t>
+        </is>
+      </c>
+      <c r="I16" s="2"/>
       <c r="J16" s="4"/>
       <c r="K16" s="2"/>
     </row>
@@ -1202,31 +1202,29 @@
         <v>2</v>
       </c>
       <c r="E17" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F17" s="2">
-        <v>1</v>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南林姑</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南林姑</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南林|姑|△</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南林
+姑
+△</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">겹쳐 적힘</t>
-        </is>
-      </c>
+      <c r="J17" s="4"/>
       <c r="K17" s="2"/>
     </row>
     <row r="18">
@@ -1239,35 +1237,37 @@
         </is>
       </c>
       <c r="C18" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F18" s="2">
         <v>1</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">林姑|姑|–</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">林姑
+姑
+–</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">아</t>
+          <t xml:space="preserve">님과</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">南 s자 꾸밈</t>
+          <t xml:space="preserve">윗줄 둘째 글자 姑/㴌?</t>
         </is>
       </c>
       <c r="K18" s="2"/>
@@ -1282,33 +1282,35 @@
         </is>
       </c>
       <c r="C19" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F19" s="2">
         <v>1</v>
       </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I19" s="3"/>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">물결선 } 요성</t>
-        </is>
-      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|南林|姑</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+南林
+姑</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아아</t>
+        </is>
+      </c>
+      <c r="J19" s="4"/>
       <c r="K19" s="2"/>
     </row>
     <row r="20">
@@ -1321,30 +1323,30 @@
         </is>
       </c>
       <c r="C20" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F20" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">아아</t>
+          <t xml:space="preserve">아</t>
         </is>
       </c>
       <c r="J20" s="4"/>
@@ -1360,33 +1362,35 @@
         </is>
       </c>
       <c r="C21" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F21" s="2">
-        <v>2</v>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢南潢</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢南潢</t>
-        </is>
-      </c>
-      <c r="I21" s="3"/>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">겹쳐 적혀 확실치 않음</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|潢|南潢</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+潢
+南潢</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아아</t>
+        </is>
+      </c>
+      <c r="J21" s="4"/>
       <c r="K21" s="2"/>
     </row>
     <row r="22">
@@ -1399,37 +1403,35 @@
         </is>
       </c>
       <c r="C22" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F22" s="2">
         <v>2</v>
       </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰潢太</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰潢太</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">날</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太 s자 꾸밈, 겹쳐 적힘</t>
-        </is>
-      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰|㴌汰|潢</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+㴌汰
+潢</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">날과</t>
+        </is>
+      </c>
+      <c r="J22" s="4"/>
       <c r="K22" s="2"/>
     </row>
     <row r="23">
@@ -1442,30 +1444,32 @@
         </is>
       </c>
       <c r="C23" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F23" s="2">
         <v>2</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">–|汰潢|南</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">–
+汰潢
+南</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">과</t>
+          <t xml:space="preserve">아아</t>
         </is>
       </c>
       <c r="J23" s="4"/>
@@ -1481,30 +1485,32 @@
         </is>
       </c>
       <c r="C24" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F24" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">–|–|南^</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">–
+–
+南^</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">아아</t>
+          <t xml:space="preserve">아</t>
         </is>
       </c>
       <c r="J24" s="4"/>
@@ -1520,28 +1526,34 @@
         </is>
       </c>
       <c r="C25" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F25" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–南林</t>
+          <t xml:space="preserve">汰|潢|南</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–南林</t>
-        </is>
-      </c>
-      <c r="I25" s="2"/>
+          <t xml:space="preserve">汰
+潢
+南</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이별얼</t>
+        </is>
+      </c>
       <c r="J25" s="4"/>
       <c r="K25" s="2"/>
     </row>
@@ -1555,34 +1567,35 @@
         </is>
       </c>
       <c r="C26" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D26" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E26" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F26" s="2">
-        <v>3</v>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|–</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|南^|潢</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–</t>
-        </is>
-      </c>
-      <c r="I26" s="3"/>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가로획 두 개(二처럼 보임)</t>
-        </is>
-      </c>
+南^
+潢</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이별</t>
+        </is>
+      </c>
+      <c r="J26" s="4"/>
       <c r="K26" s="2"/>
     </row>
     <row r="27">
@@ -1595,30 +1608,32 @@
         </is>
       </c>
       <c r="C27" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D27" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E27" s="2">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F27" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南林|姑|–</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南林
+姑
+–</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">아</t>
+          <t xml:space="preserve">이이</t>
         </is>
       </c>
       <c r="J27" s="4"/>
@@ -1634,30 +1649,31 @@
         </is>
       </c>
       <c r="C28" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D28" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E28" s="2">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F28" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南姑</t>
+          <t xml:space="preserve">南林|–</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南姑</t>
+          <t xml:space="preserve">南林
+–</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이별이</t>
+          <t xml:space="preserve">이</t>
         </is>
       </c>
       <c r="J28" s="4"/>
@@ -1673,28 +1689,32 @@
         </is>
       </c>
       <c r="C29" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D29" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E29" s="2">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F29" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I29" s="2"/>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
       <c r="J29" s="4"/>
       <c r="K29" s="2"/>
     </row>
@@ -1708,37 +1728,29 @@
         </is>
       </c>
       <c r="C30" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E30" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F30" s="2">
-        <v>1</v>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南林姑</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南林姑</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이이</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">겹쳐 적힘</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I30" s="2"/>
+      <c r="J30" s="4"/>
       <c r="K30" s="2"/>
     </row>
     <row r="31">
@@ -1751,302 +1763,34 @@
         </is>
       </c>
       <c r="C31" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D31" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F31" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I31" s="2"/>
       <c r="J31" s="4"/>
       <c r="K31" s="2"/>
     </row>
-    <row r="32">
-      <c r="A32" s="2">
-        <v>1</v>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/이별가.jpg</t>
-        </is>
-      </c>
-      <c r="C32" s="2">
-        <v>3</v>
-      </c>
-      <c r="D32" s="2">
-        <v>3</v>
-      </c>
-      <c r="E32" s="2">
-        <v>3</v>
-      </c>
-      <c r="F32" s="2">
-        <v>1</v>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南林</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南林</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
-      <c r="J32" s="4"/>
-      <c r="K32" s="2"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2">
-        <v>1</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/이별가.jpg</t>
-        </is>
-      </c>
-      <c r="C33" s="2">
-        <v>3</v>
-      </c>
-      <c r="D33" s="2">
-        <v>3</v>
-      </c>
-      <c r="E33" s="2">
-        <v>4</v>
-      </c>
-      <c r="F33" s="2">
-        <v>1</v>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I33" s="2"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="2"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2">
-        <v>1</v>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/이별가.jpg</t>
-        </is>
-      </c>
-      <c r="C34" s="2">
-        <v>3</v>
-      </c>
-      <c r="D34" s="2">
-        <v>3</v>
-      </c>
-      <c r="E34" s="2">
-        <v>5</v>
-      </c>
-      <c r="F34" s="2">
-        <v>2</v>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑 s자 꾸밈</t>
-        </is>
-      </c>
-      <c r="K34" s="2"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2">
-        <v>1</v>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/이별가.jpg</t>
-        </is>
-      </c>
-      <c r="C35" s="2">
-        <v>3</v>
-      </c>
-      <c r="D35" s="2">
-        <v>3</v>
-      </c>
-      <c r="E35" s="2">
-        <v>7</v>
-      </c>
-      <c r="F35" s="2">
-        <v>2</v>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I35" s="2"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="2"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2">
-        <v>1</v>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/이별가.jpg</t>
-        </is>
-      </c>
-      <c r="C36" s="2">
-        <v>3</v>
-      </c>
-      <c r="D36" s="2">
-        <v>3</v>
-      </c>
-      <c r="E36" s="2">
-        <v>9</v>
-      </c>
-      <c r="F36" s="2">
-        <v>3</v>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아아</t>
-        </is>
-      </c>
-      <c r="J36" s="4"/>
-      <c r="K36" s="2"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2">
-        <v>1</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/이별가.jpg</t>
-        </is>
-      </c>
-      <c r="C37" s="2">
-        <v>3</v>
-      </c>
-      <c r="D37" s="2">
-        <v>3</v>
-      </c>
-      <c r="E37" s="2">
-        <v>10</v>
-      </c>
-      <c r="F37" s="2">
-        <v>3</v>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="I37" s="2"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="2"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2">
-        <v>1</v>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/이별가.jpg</t>
-        </is>
-      </c>
-      <c r="C38" s="2">
-        <v>3</v>
-      </c>
-      <c r="D38" s="2">
-        <v>3</v>
-      </c>
-      <c r="E38" s="2">
-        <v>13</v>
-      </c>
-      <c r="F38" s="2">
-        <v>4</v>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太潢姑</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太潢姑</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이별이</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">겹쳐 적힘, 太 3자 꾸밈</t>
-        </is>
-      </c>
-      <c r="K38" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K38"/>
+  <autoFilter ref="A1:K31"/>
 </worksheet>
 </file>
 
@@ -2060,12 +1804,14 @@
     <col min="5" max="5" width="6" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="55.19" customHeight="1">
+    <row r="2" ht="81.3" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2077,280 +1823,308 @@
       <c r="E2" s="20"/>
       <c r="F2" s="20"/>
       <c r="G2" s="20"/>
-    </row>
-    <row r="3" ht="55.19" customHeight="1">
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+    </row>
+    <row r="3" ht="81.3" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南林姑</t>
-        </is>
-      </c>
-      <c r="C3" s="29" t="inlineStr">
+          <t xml:space="preserve">–
+南^
+潢</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이
+별</t>
+        </is>
+      </c>
+      <c r="D3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">林姑
+姑
+–</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">님
+과</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+–
+潢</t>
+        </is>
+      </c>
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 이</t>
         </is>
       </c>
-      <c r="D3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E3" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="F3" s="21" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">淋
+㴌
+–</t>
+        </is>
+      </c>
+      <c r="I3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이
+별</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="81.3" customHeight="1">
+      <c r="A4" s="0"/>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南林
+姑
+–</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이
+이</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-汰</t>
-        </is>
-      </c>
-      <c r="G3" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="55.19" customHeight="1">
-      <c r="A4" s="0"/>
-      <c r="B4" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南林姑</t>
-        </is>
-      </c>
-      <c r="E4" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
+南林
+姑</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아
+아</t>
         </is>
       </c>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢</t>
-        </is>
-      </c>
-      <c r="G4" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="55.19" customHeight="1">
-      <c r="A5" s="0"/>
-      <c r="B5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南林</t>
-        </is>
-      </c>
-      <c r="C5" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E5" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="F5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋潢</t>
-        </is>
-      </c>
-      <c r="G5" s="31" t="inlineStr">
+          <t xml:space="preserve">南林
+姑
+–△</t>
+        </is>
+      </c>
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 야</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="55.19" customHeight="1">
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+汰
+潢㴌</t>
+        </is>
+      </c>
+      <c r="I4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이
+이</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="81.3" customHeight="1">
+      <c r="A5" s="0"/>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南林
+–</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–
+–</t>
+        </is>
+      </c>
+      <c r="G5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">淋
+㴌
+–</t>
+        </is>
+      </c>
+      <c r="I5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이
+야</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="81.3" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C6" s="33"/>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E6" s="34"/>
-      <c r="F6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G6" s="33"/>
-    </row>
-    <row r="7" ht="55.19" customHeight="1">
+          <t xml:space="preserve">–
+潢
+南潢</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아
+아</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+–
+潢</t>
+        </is>
+      </c>
+      <c r="G6" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+汰
+潢㴌</t>
+        </is>
+      </c>
+      <c r="I6" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아
+아</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="81.3" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C7" s="29" t="inlineStr">
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="C7" s="22"/>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+㴌汰
+潢</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">날
+과</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+–潢
+南林</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E7" s="30" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+–
+–</t>
+        </is>
+      </c>
+      <c r="I7" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="81.3" customHeight="1">
+      <c r="A8" s="0"/>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="C8" s="25"/>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+汰潢
+南</t>
+        </is>
+      </c>
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 아</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-汰</t>
-        </is>
-      </c>
-      <c r="G7" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="55.19" customHeight="1">
-      <c r="A8" s="0"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢南潢</t>
-        </is>
-      </c>
-      <c r="E8" s="32"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢淋</t>
-        </is>
-      </c>
-      <c r="G8" s="32"/>
-    </row>
-    <row r="9" ht="55.19" customHeight="1">
-      <c r="A9" s="0"/>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C9" s="31"/>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰潢太</t>
-        </is>
-      </c>
-      <c r="E9" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">날</t>
-        </is>
-      </c>
-      <c r="F9" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="G9" s="31"/>
-    </row>
-    <row r="10" ht="55.19" customHeight="1">
-      <c r="A10" s="0"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E10" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">과</t>
-        </is>
-      </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G10" s="33"/>
-    </row>
-    <row r="11" ht="55.19" customHeight="1">
-      <c r="A11" s="0"/>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C11" s="30" t="inlineStr">
+          <t xml:space="preserve">姑
+–
+南林</t>
+        </is>
+      </c>
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 아</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E11" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아
-아</t>
-        </is>
-      </c>
-      <c r="F11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G11" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="55.19" customHeight="1">
-      <c r="A12" s="0"/>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="C12" s="31"/>
-      <c r="D12" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–南林</t>
-        </is>
-      </c>
-      <c r="E12" s="31"/>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋汰
-㳞</t>
-        </is>
-      </c>
-      <c r="G12" s="32" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+㴌汰
+㴌△</t>
+        </is>
+      </c>
+      <c r="I8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 아
@@ -2358,23 +2132,38 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="55.19" customHeight="1">
-      <c r="A13" s="0"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="21" t="inlineStr">
+    <row r="9" ht="81.3" customHeight="1">
+      <c r="A9" s="0"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–</t>
-        </is>
-      </c>
-      <c r="E13" s="32"/>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋潢</t>
-        </is>
-      </c>
-      <c r="G13" s="31" t="inlineStr">
+–
+南^</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+–
+△</t>
+        </is>
+      </c>
+      <c r="G9" s="25"/>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">淋
+㴌
+汰</t>
+        </is>
+      </c>
+      <c r="I9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 별
@@ -2382,111 +2171,57 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="55.19" customHeight="1">
-      <c r="A14" s="0"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E14" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="G14" s="34"/>
-    </row>
-    <row r="15" ht="55.19" customHeight="1">
-      <c r="A15" s="0"/>
-      <c r="B15" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太潢姑</t>
-        </is>
-      </c>
-      <c r="C15" s="29" t="inlineStr">
+    <row r="10" ht="81.3" customHeight="1">
+      <c r="A10" s="0"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+潢
+南</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 별
-이</t>
-        </is>
-      </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南姑</t>
-        </is>
-      </c>
-      <c r="E15" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이
-별
-이</t>
-        </is>
-      </c>
-      <c r="F15" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G15" s="30" t="inlineStr">
+얼</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南林
+姑
+△</t>
+        </is>
+      </c>
+      <c r="G10" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+潢
+㴌</t>
+        </is>
+      </c>
+      <c r="I10" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 이
-야</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="55.19" customHeight="1">
-      <c r="A16" s="0"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E16" s="31"/>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢潢</t>
-        </is>
-      </c>
-      <c r="G16" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="55.19" customHeight="1">
-      <c r="A17" s="0"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="31"/>
-    </row>
-    <row r="18" ht="55.19" customHeight="1">
-      <c r="A18" s="0"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="33"/>
+이</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B2:I2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/이별가.xlsx
+++ b/sheets/민요/검수/이별가.xlsx
@@ -65,10 +65,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">

--- a/sheets/민요/검수/이별가.xlsx
+++ b/sheets/민요/검수/이별가.xlsx
@@ -1793,6 +1793,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1805,10 +1808,10 @@
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="81.3" customHeight="1">
+    <row r="2" ht="43.01" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -1823,7 +1826,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="81.3" customHeight="1">
+    <row r="3" ht="95.8" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -1878,7 +1881,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="81.3" customHeight="1">
+    <row r="4" ht="95.8" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -1933,7 +1936,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="81.3" customHeight="1">
+    <row r="5" ht="95.8" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -1982,7 +1985,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="81.3" customHeight="1">
+    <row r="6" ht="95.8" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2033,7 +2036,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="81.3" customHeight="1">
+    <row r="7" ht="95.8" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2079,7 +2082,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="81.3" customHeight="1">
+    <row r="8" ht="95.8" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2129,7 +2132,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="81.3" customHeight="1">
+    <row r="9" ht="95.8" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="25"/>
@@ -2168,7 +2171,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="81.3" customHeight="1">
+    <row r="10" ht="95.8" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="26"/>
@@ -2219,6 +2222,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="93"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/이별가.xlsx
+++ b/sheets/민요/검수/이별가.xlsx
@@ -1798,13 +1798,13 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
